--- a/design/武器表.xlsx
+++ b/design/武器表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="武器|Weapon" sheetId="1" r:id="rId1"/>
@@ -243,7 +243,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="88">
   <si>
     <t>武器配置ID</t>
   </si>
@@ -335,6 +335,9 @@
     <t>灰盒步枪</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>50</t>
   </si>
   <si>
@@ -366,9 +369,6 @@
   </si>
   <si>
     <t>12</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
   <si>
     <t>5|6</t>
@@ -737,7 +737,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="39">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -765,12 +765,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF3F6FA"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="1" tint="0.5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1151,7 +1145,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1175,16 +1169,16 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1193,85 +1187,85 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1346,7 +1340,7 @@
     <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="7" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="6" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1999,34 +1993,36 @@
       <c r="B5" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="18"/>
+      <c r="C5" s="18" t="s">
+        <v>30</v>
+      </c>
       <c r="D5" s="19"/>
       <c r="E5" s="18" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F5" s="18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G5" s="18" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H5" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I5" s="19" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J5" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="K5" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="K5" s="18" t="s">
-        <v>34</v>
-      </c>
       <c r="L5" s="19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1" spans="1:14">
@@ -2034,30 +2030,32 @@
         <v>2</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
-      <c r="C6" s="20"/>
+      <c r="C6" s="20" t="s">
+        <v>30</v>
+      </c>
       <c r="D6" s="19"/>
       <c r="E6" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="H6" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="I6" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="F6" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="G6" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="H6" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="I6" s="19" t="s">
-        <v>41</v>
-      </c>
       <c r="J6" s="20" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K6" s="20" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="L6" s="19" t="s">
         <v>42</v>
@@ -2070,22 +2068,24 @@
       <c r="B7" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="C7" s="24"/>
+      <c r="C7" s="24" t="s">
+        <v>35</v>
+      </c>
       <c r="D7" s="25"/>
       <c r="E7" s="24" t="s">
         <v>45</v>
       </c>
       <c r="F7" s="24" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G7" s="24" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H7" s="24" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I7" s="19" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J7" s="18" t="s">
         <v>46</v>
@@ -9170,7 +9170,7 @@
         <v>68</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D5" s="18" t="s">
         <v>69</v>
@@ -9179,29 +9179,29 @@
         <v>70</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G5" s="18" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H5" s="18" t="s">
         <v>71</v>
       </c>
       <c r="I5" s="18" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J5" s="18"/>
       <c r="K5" s="19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L5" s="18" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M5" s="19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P5" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1" spans="1:16">
@@ -9212,19 +9212,19 @@
         <v>72</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D6" s="20" t="s">
         <v>73</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G6" s="20" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H6" s="20">
         <v>1000</v>
@@ -9237,10 +9237,10 @@
         <v>74</v>
       </c>
       <c r="L6" s="20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M6" s="19" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" customFormat="1" ht="26" customHeight="1" spans="1:16">
@@ -9251,7 +9251,7 @@
         <v>75</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D7" s="18" t="s">
         <v>76</v>
@@ -9260,16 +9260,16 @@
         <v>70</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G7" s="18" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H7" s="18" t="s">
         <v>71</v>
       </c>
       <c r="I7" s="18" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J7" s="18"/>
       <c r="K7" s="19" t="s">
@@ -9279,10 +9279,10 @@
         <v>46</v>
       </c>
       <c r="M7" s="19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P7" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -16752,7 +16752,7 @@
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
       <c r="H5" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1" spans="1:8">
@@ -16790,7 +16790,7 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>87</v>

--- a/design/武器表.xlsx
+++ b/design/武器表.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\聚光灯\Hunter\design\"/>
+      <x15ac:absPath url="E:\聚光灯\Hunter\design\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+    <ext uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:Single"/>
@@ -541,14 +541,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="63">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -765,8 +765,178 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Microsoft YaHei UI"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF12283F"/>
+      <name val="Microsoft YaHei UI"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF79511F"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF79511F"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF202C3A"/>
+      <name val="Microsoft YaHei UI"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF12283F"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF202C3A"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF20364D"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF20364D"/>
+      <name val="Carlito"/>
+    </font>
   </fonts>
-  <fills count="38">
+  <fills count="75">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -989,8 +1159,193 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB9CEE3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF0CF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3F6FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDD3E7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="13">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -1148,8 +1503,132 @@
       </bottom>
       <diagonal/>
     </border>
+    <border/>
+    <border>
+      <right style="thin">
+        <color rgb="FFE7EFF7"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="FFE7EFF7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE7EFF7"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE7EFF7"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="FFE7EFF7"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FFE7EFF7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE7EFF7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE7EFF7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE7EFF7"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE7EFF7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE7EFF7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE7EFF7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="medium">
+        <color theme="4" tint="0.49998"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+    </border>
+    <border>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+    </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1298,8 +1777,156 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="13">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="40" fillId="0" borderId="13" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="40" fillId="0" borderId="13" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="40" fillId="0" borderId="13" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="40" fillId="0" borderId="13" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="40" fillId="0" borderId="13" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="43" borderId="18" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="44" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="45" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="45" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="46" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="47" borderId="13" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="48" borderId="13" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="49" borderId="13" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="50" borderId="13" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="51" borderId="13" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="52" borderId="13" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="53" borderId="13" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="54" borderId="13" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="55" borderId="13" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="56" borderId="13" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="57" borderId="13" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="58" borderId="13" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="59" borderId="13" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="60" borderId="13" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="61" borderId="13" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="62" borderId="13" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="63" borderId="13" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="64" borderId="13" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="65" borderId="13" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="66" borderId="13" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="67" borderId="13" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="68" borderId="13" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="69" borderId="13" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="70" borderId="13" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="71" borderId="13" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="72" borderId="13" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="73" borderId="13" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="13"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1371,6 +1998,110 @@
     </xf>
     <xf numFmtId="49" fontId="8" fillId="6" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="13" xfId="99"/>
+    <xf numFmtId="49" fontId="32" fillId="0" borderId="13" xfId="99" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="33" fillId="38" borderId="14" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="33" fillId="38" borderId="15" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="39" borderId="13" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="33" fillId="38" borderId="16" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="33" fillId="38" borderId="17" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="13" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="36" fillId="40" borderId="13" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="36" fillId="41" borderId="13" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="32" fillId="0" borderId="13" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="31" fillId="0" borderId="13" xfId="99" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="37" fillId="38" borderId="14" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="37" fillId="38" borderId="15" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="37" fillId="42" borderId="15" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="37" fillId="38" borderId="16" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="37" fillId="38" borderId="17" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="37" fillId="42" borderId="17" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="38" fillId="40" borderId="13" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="38" fillId="42" borderId="13" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="38" fillId="41" borderId="13" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="31" fillId="0" borderId="13" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="0" borderId="13" xfId="99" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="37" fillId="42" borderId="16" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="0" borderId="13" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="42" borderId="13" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="37" fillId="74" borderId="15" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="37" fillId="74" borderId="16" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="37" fillId="74" borderId="17" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="61" fillId="74" borderId="15" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="61" fillId="74" borderId="16" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="61" fillId="74" borderId="17" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="61" fillId="74" borderId="16" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="61" fillId="74" borderId="17" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="74" borderId="13" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="62" fillId="74" borderId="13" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="62" fillId="74" borderId="13" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="74" borderId="13" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -1641,7 +2372,7 @@
     </tableStyle>
   </tableStyles>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
   </extLst>
@@ -1845,7 +2576,7 @@
   <sheetPr>
     <tabColor rgb="FF577A9A"/>
   </sheetPr>
-  <dimension ref="A1:P498"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="18.25" style="22" customWidth="1"/>
@@ -1966,7 +2697,9 @@
       <c r="D3" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="17"/>
+      <c r="E3" s="59" t="str">
+        <v>DamageType</v>
+      </c>
       <c r="F3" s="16" t="s">
         <v>22</v>
       </c>
@@ -2009,7 +2742,9 @@
       <c r="D4" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="E4" s="17"/>
+      <c r="E4" s="59" t="str">
+        <v>server/client</v>
+      </c>
       <c r="F4" s="16" t="s">
         <v>32</v>
       </c>
@@ -2052,7 +2787,9 @@
       <c r="D5" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="E5" s="19"/>
+      <c r="E5" s="45" t="n">
+        <v>1</v>
+      </c>
       <c r="F5" s="18" t="s">
         <v>36</v>
       </c>
@@ -2077,8 +2814,8 @@
       <c r="M5" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="N5" s="19" t="s">
-        <v>43</v>
+      <c r="N5" s="45" t="n">
+        <v>1</v>
       </c>
       <c r="P5" s="7" t="s">
         <v>44</v>
@@ -2097,7 +2834,9 @@
       <c r="D6" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="E6" s="19"/>
+      <c r="E6" s="45" t="n">
+        <v>1</v>
+      </c>
       <c r="F6" s="20" t="s">
         <v>36</v>
       </c>
@@ -2122,8 +2861,8 @@
       <c r="M6" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="N6" s="19" t="s">
-        <v>48</v>
+      <c r="N6" s="45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2139,7 +2878,9 @@
       <c r="D7" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="E7" s="25"/>
+      <c r="E7" s="51" t="n">
+        <v>1</v>
+      </c>
       <c r="F7" s="24" t="s">
         <v>51</v>
       </c>
@@ -2164,7 +2905,9 @@
       <c r="M7" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="N7" s="19"/>
+      <c r="N7" s="45" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="24"/>
@@ -10034,7 +10777,7 @@
   <sheetPr>
     <tabColor rgb="FF577A9A"/>
   </sheetPr>
-  <dimension ref="A1:Q498"/>
+  <dimension ref="A1:Q7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="18.25" style="11" customWidth="1"/>
@@ -10045,6 +10788,7 @@
     <col min="12" max="13" width="15.625" style="11" customWidth="1"/>
     <col min="14" max="14" width="17.75" style="11" customWidth="1"/>
     <col min="17" max="17" width="55" customWidth="1"/>
+    <col min="15" max="15" width="22" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1" spans="1:17">
@@ -10069,8 +10813,8 @@
       <c r="G1" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="H1" s="14" t="s">
-        <v>59</v>
+      <c r="H1" s="55" t="str">
+        <v>距离伤害削减（预留）</v>
       </c>
       <c r="I1" s="13" t="s">
         <v>60</v>
@@ -10089,6 +10833,9 @@
       </c>
       <c r="N1" s="14" t="s">
         <v>65</v>
+      </c>
+      <c r="O1" s="63" t="str">
+        <v>物品配置ID</v>
       </c>
       <c r="Q1" s="4" t="s">
         <v>14</v>
@@ -10137,6 +10884,9 @@
       <c r="N2" s="17" t="s">
         <v>15</v>
       </c>
+      <c r="O2" s="63" t="str">
+        <v>int32</v>
+      </c>
       <c r="Q2" s="7" t="s">
         <v>17</v>
       </c>
@@ -10157,11 +10907,15 @@
       <c r="E3" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="F3" s="17"/>
+      <c r="F3" s="59" t="str">
+        <v>DamageType</v>
+      </c>
       <c r="G3" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="H3" s="17"/>
+      <c r="H3" s="59" t="str">
+        <v>DistanceLoss</v>
+      </c>
       <c r="I3" s="16" t="s">
         <v>71</v>
       </c>
@@ -10171,12 +10925,17 @@
       <c r="K3" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="L3" s="17"/>
+      <c r="L3" s="59" t="str">
+        <v>PropDamage</v>
+      </c>
       <c r="M3" s="16" t="s">
         <v>74</v>
       </c>
       <c r="N3" s="17" t="s">
         <v>75</v>
+      </c>
+      <c r="O3" s="63" t="str">
+        <v>ItemIdx</v>
       </c>
       <c r="Q3" s="7"/>
     </row>
@@ -10202,7 +10961,9 @@
       <c r="G4" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="H4" s="17"/>
+      <c r="H4" s="59" t="str">
+        <v>server/client</v>
+      </c>
       <c r="I4" s="16" t="s">
         <v>32</v>
       </c>
@@ -10220,6 +10981,9 @@
       </c>
       <c r="N4" s="17" t="s">
         <v>32</v>
+      </c>
+      <c r="O4" s="63" t="str">
+        <v>server/client</v>
       </c>
       <c r="Q4" s="7"/>
     </row>
@@ -10242,8 +11006,8 @@
       <c r="F5" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="18" t="s">
-        <v>35</v>
+      <c r="G5" s="44" t="n">
+        <v>18000</v>
       </c>
       <c r="H5" s="19"/>
       <c r="I5" s="18" t="s">
@@ -10252,15 +11016,20 @@
       <c r="J5" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="K5" s="18"/>
+      <c r="K5" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="L5" s="19" t="s">
         <v>42</v>
       </c>
       <c r="M5" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="N5" s="19" t="s">
-        <v>36</v>
+      <c r="N5" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>20001</v>
       </c>
       <c r="Q5" s="7" t="s">
         <v>44</v>
@@ -10285,8 +11054,8 @@
       <c r="F6" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="G6" s="20" t="s">
-        <v>41</v>
+      <c r="G6" s="46" t="n">
+        <v>6000</v>
       </c>
       <c r="H6" s="19"/>
       <c r="I6" s="20">
@@ -10295,15 +11064,20 @@
       <c r="J6" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="K6" s="20"/>
+      <c r="K6" s="46" t="n">
+        <v>0</v>
+      </c>
       <c r="L6" s="19" t="s">
         <v>82</v>
       </c>
       <c r="M6" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="N6" s="19" t="s">
-        <v>39</v>
+      <c r="N6" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>20002</v>
       </c>
     </row>
     <row r="7" customFormat="1" ht="26" customHeight="1" spans="1:17">
@@ -10325,8 +11099,8 @@
       <c r="F7" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="G7" s="18" t="s">
-        <v>35</v>
+      <c r="G7" s="44" t="n">
+        <v>12000</v>
       </c>
       <c r="H7" s="19"/>
       <c r="I7" s="18" t="s">
@@ -10335,15 +11109,20 @@
       <c r="J7" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="K7" s="18"/>
+      <c r="K7" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="L7" s="19" t="s">
         <v>85</v>
       </c>
       <c r="M7" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="N7" s="19" t="s">
-        <v>36</v>
+      <c r="N7" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>20003</v>
       </c>
       <c r="Q7" s="7" t="s">
         <v>44</v>

--- a/design/武器表.xlsx
+++ b/design/武器表.xlsx
@@ -775,7 +775,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="63">
+  <fonts count="64">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -1161,6 +1161,12 @@
       <sz val="11"/>
       <color rgb="FF20364D"/>
       <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF20364D"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="75">
@@ -2153,7 +2159,7 @@
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="13"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2347,6 +2353,37 @@
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="0" borderId="13" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="74" borderId="13" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="13" xfId="99" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="31" fillId="0" borderId="13" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="32" fillId="0" borderId="13" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="63" fillId="74" borderId="15" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="63" fillId="74" borderId="17" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="63" fillId="74" borderId="17" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="74" borderId="13" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="63" fillId="74" borderId="13" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="74" borderId="13" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -11022,18 +11059,19 @@
   <sheetPr>
     <tabColor rgb="FF577A9A"/>
   </sheetPr>
-  <dimension ref="A1:Q498"/>
+  <dimension ref="A1:Q7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="18.25" style="11" customWidth="1"/>
     <col min="2" max="6" width="13.5" style="11" customWidth="1"/>
     <col min="7" max="7" width="15.625" style="11" customWidth="1"/>
     <col min="8" max="10" width="13.5" style="11" customWidth="1"/>
-    <col min="11" max="11" width="14.125" style="11" customWidth="1"/>
+    <col min="11" max="11" width="22" style="11" customWidth="1"/>
     <col min="12" max="13" width="15.625" style="11" customWidth="1"/>
     <col min="14" max="14" width="17.75" style="11" customWidth="1"/>
+    <col min="15" max="15" width="22" hidden="0" customWidth="1"/>
+    <col min="16" max="16" width="22" hidden="0" customWidth="1"/>
     <col min="17" max="17" width="55" customWidth="1"/>
-    <col min="15" max="15" width="22" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1" spans="1:17">
@@ -11067,8 +11105,8 @@
       <c r="J1" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="K1" s="13" t="s">
-        <v>62</v>
+      <c r="K1" s="75" t="str">
+        <v>可穿透场景ID（|分隔，0为无）</v>
       </c>
       <c r="L1" s="14" t="s">
         <v>63</v>
@@ -11081,6 +11119,9 @@
       </c>
       <c r="O1" s="66" t="str">
         <v>物品配置ID</v>
+      </c>
+      <c r="P1" s="80" t="str">
+        <v>每弹种单次补给量</v>
       </c>
       <c r="Q1" s="4" t="s">
         <v>14</v>
@@ -11117,8 +11158,8 @@
       <c r="J2" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="K2" s="16" t="s">
-        <v>15</v>
+      <c r="K2" s="77" t="str">
+        <v>string</v>
       </c>
       <c r="L2" s="17" t="s">
         <v>15</v>
@@ -11130,6 +11171,9 @@
         <v>15</v>
       </c>
       <c r="O2" s="66" t="str">
+        <v>int32</v>
+      </c>
+      <c r="P2" s="80" t="str">
         <v>int32</v>
       </c>
       <c r="Q2" s="7" t="s">
@@ -11182,6 +11226,9 @@
       <c r="O3" s="66" t="str">
         <v>ItemIdx</v>
       </c>
+      <c r="P3" s="80" t="str">
+        <v>RefillCount</v>
+      </c>
       <c r="Q3" s="7"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:17">
@@ -11230,6 +11277,9 @@
       <c r="O4" s="66" t="str">
         <v>server/client</v>
       </c>
+      <c r="P4" s="80" t="str">
+        <v>server/client</v>
+      </c>
       <c r="Q4" s="7"/>
     </row>
     <row r="5" ht="26" customHeight="1" spans="1:17">
@@ -11261,8 +11311,8 @@
       <c r="J5" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="K5" s="44" t="n">
-        <v>0</v>
+      <c r="K5" s="44" t="str">
+        <v>3</v>
       </c>
       <c r="L5" s="19" t="s">
         <v>42</v>
@@ -11275,6 +11325,9 @@
       </c>
       <c r="O5" t="n" s="67">
         <v>20001</v>
+      </c>
+      <c r="P5" t="n">
+        <v>5</v>
       </c>
       <c r="Q5" s="7" t="s">
         <v>44</v>
@@ -11309,7 +11362,7 @@
       <c r="J6" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="K6" s="46" t="n">
+      <c r="K6" s="46" t="str">
         <v>0</v>
       </c>
       <c r="L6" s="19" t="s">
@@ -11323,6 +11376,9 @@
       </c>
       <c r="O6" t="n" s="67">
         <v>20002</v>
+      </c>
+      <c r="P6" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="7" customFormat="1" ht="26" customHeight="1" spans="1:17">
@@ -11354,8 +11410,8 @@
       <c r="J7" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="K7" s="44" t="n">
-        <v>0</v>
+      <c r="K7" s="44" t="str">
+        <v>3</v>
       </c>
       <c r="L7" s="19" t="s">
         <v>85</v>
@@ -11368,6 +11424,9 @@
       </c>
       <c r="O7" t="n" s="67">
         <v>20003</v>
+      </c>
+      <c r="P7" t="n">
+        <v>6</v>
       </c>
       <c r="Q7" s="7" t="s">
         <v>44</v>
@@ -19732,7 +19791,7 @@
   <sheetPr>
     <tabColor theme="1" tint="0.5"/>
   </sheetPr>
-  <dimension ref="A1:H498"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="18.25" style="1" customWidth="1"/>
@@ -19800,15 +19859,9 @@
       <c r="B4" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>32</v>
-      </c>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
       <c r="H4" s="7"/>
     </row>
     <row r="5" ht="26" customHeight="1" spans="1:8">
